--- a/artfynd/A 31341-2026 artfynd.xlsx
+++ b/artfynd/A 31341-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136156609</v>
       </c>
       <c r="B2" t="n">
-        <v>92118</v>
+        <v>92119</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136156619</v>
       </c>
       <c r="B3" t="n">
-        <v>93388</v>
+        <v>93389</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 31341-2026 artfynd.xlsx
+++ b/artfynd/A 31341-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136156609</v>
       </c>
       <c r="B2" t="n">
-        <v>92119</v>
+        <v>92120</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136156619</v>
       </c>
       <c r="B3" t="n">
-        <v>93389</v>
+        <v>93390</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136156606</v>
       </c>
       <c r="B4" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136156607</v>
       </c>
       <c r="B5" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136156608</v>
       </c>
       <c r="B6" t="n">
-        <v>80034</v>
+        <v>80035</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 31341-2026 artfynd.xlsx
+++ b/artfynd/A 31341-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136156609</v>
       </c>
       <c r="B2" t="n">
-        <v>92120</v>
+        <v>92126</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136156619</v>
       </c>
       <c r="B3" t="n">
-        <v>93390</v>
+        <v>93396</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136156606</v>
       </c>
       <c r="B4" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136156607</v>
       </c>
       <c r="B5" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136156608</v>
       </c>
       <c r="B6" t="n">
-        <v>80035</v>
+        <v>80039</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 31341-2026 artfynd.xlsx
+++ b/artfynd/A 31341-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136156609</v>
       </c>
       <c r="B2" t="n">
-        <v>92126</v>
+        <v>92127</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136156619</v>
       </c>
       <c r="B3" t="n">
-        <v>93396</v>
+        <v>93397</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136156606</v>
       </c>
       <c r="B4" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136156607</v>
       </c>
       <c r="B5" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136156608</v>
       </c>
       <c r="B6" t="n">
-        <v>80039</v>
+        <v>80040</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 31341-2026 artfynd.xlsx
+++ b/artfynd/A 31341-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136156609</v>
       </c>
       <c r="B2" t="n">
-        <v>92127</v>
+        <v>92133</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136156619</v>
       </c>
       <c r="B3" t="n">
-        <v>93397</v>
+        <v>93403</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136156606</v>
       </c>
       <c r="B4" t="n">
-        <v>80069</v>
+        <v>80073</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136156607</v>
       </c>
       <c r="B5" t="n">
-        <v>80069</v>
+        <v>80073</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136156608</v>
       </c>
       <c r="B6" t="n">
-        <v>80040</v>
+        <v>80044</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 31341-2026 artfynd.xlsx
+++ b/artfynd/A 31341-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136156609</v>
       </c>
       <c r="B2" t="n">
-        <v>92133</v>
+        <v>92140</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136156619</v>
       </c>
       <c r="B3" t="n">
-        <v>93403</v>
+        <v>93410</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136156606</v>
       </c>
       <c r="B4" t="n">
-        <v>80073</v>
+        <v>80079</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136156607</v>
       </c>
       <c r="B5" t="n">
-        <v>80073</v>
+        <v>80079</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136156608</v>
       </c>
       <c r="B6" t="n">
-        <v>80044</v>
+        <v>80050</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 31341-2026 artfynd.xlsx
+++ b/artfynd/A 31341-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136156609</v>
       </c>
       <c r="B2" t="n">
-        <v>92140</v>
+        <v>92141</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136156619</v>
       </c>
       <c r="B3" t="n">
-        <v>93410</v>
+        <v>93411</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 31341-2026 artfynd.xlsx
+++ b/artfynd/A 31341-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136156609</v>
       </c>
       <c r="B2" t="n">
-        <v>92141</v>
+        <v>92154</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136156619</v>
       </c>
       <c r="B3" t="n">
-        <v>93411</v>
+        <v>93424</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136156606</v>
       </c>
       <c r="B4" t="n">
-        <v>80079</v>
+        <v>80092</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136156607</v>
       </c>
       <c r="B5" t="n">
-        <v>80079</v>
+        <v>80092</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136156608</v>
       </c>
       <c r="B6" t="n">
-        <v>80050</v>
+        <v>80063</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 31341-2026 artfynd.xlsx
+++ b/artfynd/A 31341-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136156609</v>
       </c>
       <c r="B2" t="n">
-        <v>92154</v>
+        <v>92155</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136156619</v>
       </c>
       <c r="B3" t="n">
-        <v>93424</v>
+        <v>93425</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136156606</v>
       </c>
       <c r="B4" t="n">
-        <v>80092</v>
+        <v>80093</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136156607</v>
       </c>
       <c r="B5" t="n">
-        <v>80092</v>
+        <v>80093</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136156608</v>
       </c>
       <c r="B6" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
